--- a/public/inputs/y10-spanish-1st-igcse - input.xlsx
+++ b/public/inputs/y10-spanish-1st-igcse - input.xlsx
@@ -444,7 +444,6 @@
           <t>Unidad 1 · Leer para Comprender</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -454,10 +453,9 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unidad 2 · Leer entre Líneas: Inferenciay</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>Unidad 2 · Leer entre Líneas: Inferencia y</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -467,10 +465,9 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unidad 3 · España: Lengua, Culturae Identidad</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>Unidad 3 · España: Lengua, Cultura e Identidad</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -480,10 +477,9 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unidad 4 · Selección de Información, Síntesisy</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>Unidad 4 · Selección de Información, Síntesis y</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,10 +489,9 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unidad 5 · Escritura Dirigida: de las Fuentesa la</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>Unidad 5 · Escritura Dirigida: de las Fuentes a la</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -509,7 +504,6 @@
           <t>Unidad 6 · Gramática para Escribir Mejor</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -519,10 +513,9 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unidad 7 · Historia de Españaa través de los</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>Unidad 7 · Historia de España a través de los</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -532,10 +525,9 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unidad 8 · Escritura Argumentativay Discursiva</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>Unidad 8 · Escritura Argumentativa y Discursiva</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -548,7 +540,6 @@
           <t>Unidad 9 · Escritura Descriptiva</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -561,7 +552,6 @@
           <t>Unidad 10 · Escritura Narrativa</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -571,10 +561,9 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unidad 11 · Literatura Española: Leer, Sentiry</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>Unidad 11 · Literatura Española: Leer, Sentir y</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -587,7 +576,6 @@
           <t>Unidad 12 · Práctica de Examen · Year 10</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -600,7 +588,6 @@
           <t>Unidad 13 · Leer como un Examinador</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -610,10 +597,9 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unidad 14 · Lenguaje, Podery Persuasión</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>Unidad 14 · Lenguaje, Poder y Persuasión</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -623,10 +609,9 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unidad 15 · Síntesisy Paráfrasis Avanzadas</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>Unidad 15 · Síntesis y Paráfrasis Avanzadas</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -639,7 +624,6 @@
           <t>Unidad 16 · Escritura Dirigida Avanzada</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -652,7 +636,6 @@
           <t>Unidad 17 · España en Transformación</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -665,7 +648,6 @@
           <t>Unidad 18 · Grandes Voces de la Literatura</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -678,7 +660,6 @@
           <t>Unidad 19 · Dominar la Escritura Argumentativa</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -691,7 +672,6 @@
           <t>Unidad 20 · Dominar la Escritura Descriptiva</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -704,7 +684,6 @@
           <t>Unidad 21 · Dominar la Escritura Narrativa</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -717,7 +696,6 @@
           <t>Unidad 22 · Dominio de la Lengua Española</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -730,7 +708,6 @@
           <t>Unidad 23 · Pensar como un Examinador</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -743,7 +720,6 @@
           <t>Unidad 24 · Práctica Intensiva de Examen</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -756,7 +732,6 @@
           <t>Unidad 25 · Simulacros de Examen</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -769,7 +744,6 @@
           <t>Unidad 26 · Repaso Final IGCSE</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
